--- a/outputs/2026-10-03-dummy-datasets/dummy-data-monitoring-surat-disposisi.xlsx
+++ b/outputs/2026-10-03-dummy-datasets/dummy-data-monitoring-surat-disposisi.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R22c432d65b764cdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panduan" sheetId="2" r:id="R5496af96be934431"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rbc768d0159554086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panduan" sheetId="2" r:id="R1516e5d9bb0442ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -73,6 +73,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -215,7 +220,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="48">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -328,8 +333,13 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -653,7 +663,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F3" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -661,9 +671,7 @@
       <x:c r="H3" s="22" t="n">
         <x:v>46131</x:v>
       </x:c>
-      <x:c r="I3" s="22" t="n">
-        <x:v>46131</x:v>
-      </x:c>
+      <x:c r="I3" s="22" t="str"/>
       <x:c r="J3" s="25" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -688,7 +696,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F4" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G4" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -696,9 +704,7 @@
       <x:c r="H4" s="22" t="n">
         <x:v>46136</x:v>
       </x:c>
-      <x:c r="I4" s="22" t="n">
-        <x:v>46138</x:v>
-      </x:c>
+      <x:c r="I4" s="22" t="str"/>
       <x:c r="J4" s="25" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -731,9 +737,7 @@
       <x:c r="H5" s="22" t="n">
         <x:v>46141</x:v>
       </x:c>
-      <x:c r="I5" s="22" t="n">
-        <x:v>46136</x:v>
-      </x:c>
+      <x:c r="I5" s="22" t="str"/>
       <x:c r="J5" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -758,7 +762,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F6" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G6" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -793,7 +797,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F7" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G7" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -801,9 +805,7 @@
       <x:c r="H7" s="22" t="n">
         <x:v>46143</x:v>
       </x:c>
-      <x:c r="I7" s="22" t="n">
-        <x:v>46141</x:v>
-      </x:c>
+      <x:c r="I7" s="22" t="str"/>
       <x:c r="J7" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -836,9 +838,7 @@
       <x:c r="H8" s="22" t="n">
         <x:v>46148</x:v>
       </x:c>
-      <x:c r="I8" s="22" t="n">
-        <x:v>46148</x:v>
-      </x:c>
+      <x:c r="I8" s="22" t="str"/>
       <x:c r="J8" s="25" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -863,7 +863,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F9" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G9" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -871,9 +871,7 @@
       <x:c r="H9" s="22" t="n">
         <x:v>46153</x:v>
       </x:c>
-      <x:c r="I9" s="22" t="n">
-        <x:v>46146</x:v>
-      </x:c>
+      <x:c r="I9" s="22" t="str"/>
       <x:c r="J9" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -898,7 +896,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F10" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G10" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -941,9 +939,7 @@
       <x:c r="H11" s="22" t="n">
         <x:v>46155</x:v>
       </x:c>
-      <x:c r="I11" s="22" t="n">
-        <x:v>46151</x:v>
-      </x:c>
+      <x:c r="I11" s="22" t="str"/>
       <x:c r="J11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -968,7 +964,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F12" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G12" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -976,9 +972,7 @@
       <x:c r="H12" s="22" t="n">
         <x:v>46160</x:v>
       </x:c>
-      <x:c r="I12" s="22" t="n">
-        <x:v>46158</x:v>
-      </x:c>
+      <x:c r="I12" s="22" t="str"/>
       <x:c r="J12" s="25" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -1003,7 +997,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F13" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G13" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -1011,9 +1005,7 @@
       <x:c r="H13" s="22" t="n">
         <x:v>46165</x:v>
       </x:c>
-      <x:c r="I13" s="22" t="n">
-        <x:v>46165</x:v>
-      </x:c>
+      <x:c r="I13" s="22" t="str"/>
       <x:c r="J13" s="25" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -1073,7 +1065,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F15" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G15" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -1081,9 +1073,7 @@
       <x:c r="H15" s="22" t="n">
         <x:v>46167</x:v>
       </x:c>
-      <x:c r="I15" s="22" t="n">
-        <x:v>46170</x:v>
-      </x:c>
+      <x:c r="I15" s="22" t="str"/>
       <x:c r="J15" s="25" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -1108,7 +1098,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F16" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G16" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -1116,9 +1106,7 @@
       <x:c r="H16" s="22" t="n">
         <x:v>46172</x:v>
       </x:c>
-      <x:c r="I16" s="22" t="n">
-        <x:v>46168</x:v>
-      </x:c>
+      <x:c r="I16" s="22" t="str"/>
       <x:c r="J16" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1151,9 +1139,7 @@
       <x:c r="H17" s="22" t="n">
         <x:v>46177</x:v>
       </x:c>
-      <x:c r="I17" s="22" t="n">
-        <x:v>46175</x:v>
-      </x:c>
+      <x:c r="I17" s="22" t="str"/>
       <x:c r="J17" s="25" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -1178,7 +1164,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F18" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G18" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -1213,7 +1199,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F19" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G19" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -1221,9 +1207,7 @@
       <x:c r="H19" s="22" t="n">
         <x:v>46179</x:v>
       </x:c>
-      <x:c r="I19" s="22" t="n">
-        <x:v>46180</x:v>
-      </x:c>
+      <x:c r="I19" s="22" t="str"/>
       <x:c r="J19" s="25" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -1256,9 +1240,7 @@
       <x:c r="H20" s="22" t="n">
         <x:v>46184</x:v>
       </x:c>
-      <x:c r="I20" s="22" t="n">
-        <x:v>46178</x:v>
-      </x:c>
+      <x:c r="I20" s="22" t="str"/>
       <x:c r="J20" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1283,7 +1265,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F21" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G21" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -1291,9 +1273,7 @@
       <x:c r="H21" s="22" t="n">
         <x:v>46189</x:v>
       </x:c>
-      <x:c r="I21" s="22" t="n">
-        <x:v>46185</x:v>
-      </x:c>
+      <x:c r="I21" s="22" t="str"/>
       <x:c r="J21" s="25" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -1318,7 +1298,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F22" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G22" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -1361,9 +1341,7 @@
       <x:c r="H23" s="22" t="n">
         <x:v>46191</x:v>
       </x:c>
-      <x:c r="I23" s="22" t="n">
-        <x:v>46190</x:v>
-      </x:c>
+      <x:c r="I23" s="22" t="str"/>
       <x:c r="J23" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -1388,7 +1366,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F24" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G24" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -1396,9 +1374,7 @@
       <x:c r="H24" s="22" t="n">
         <x:v>46196</x:v>
       </x:c>
-      <x:c r="I24" s="22" t="n">
-        <x:v>46197</x:v>
-      </x:c>
+      <x:c r="I24" s="22" t="str"/>
       <x:c r="J24" s="25" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -1423,7 +1399,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F25" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G25" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -1431,9 +1407,7 @@
       <x:c r="H25" s="22" t="n">
         <x:v>46201</x:v>
       </x:c>
-      <x:c r="I25" s="22" t="n">
-        <x:v>46195</x:v>
-      </x:c>
+      <x:c r="I25" s="22" t="str"/>
       <x:c r="J25" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1493,7 +1467,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F27" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G27" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -1501,9 +1475,7 @@
       <x:c r="H27" s="22" t="n">
         <x:v>46203</x:v>
       </x:c>
-      <x:c r="I27" s="22" t="n">
-        <x:v>46200</x:v>
-      </x:c>
+      <x:c r="I27" s="22" t="str"/>
       <x:c r="J27" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -1528,7 +1500,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F28" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G28" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -1536,9 +1508,7 @@
       <x:c r="H28" s="22" t="n">
         <x:v>46208</x:v>
       </x:c>
-      <x:c r="I28" s="22" t="n">
-        <x:v>46207</x:v>
-      </x:c>
+      <x:c r="I28" s="22" t="str"/>
       <x:c r="J28" s="25" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -1571,9 +1541,7 @@
       <x:c r="H29" s="22" t="n">
         <x:v>46213</x:v>
       </x:c>
-      <x:c r="I29" s="22" t="n">
-        <x:v>46205</x:v>
-      </x:c>
+      <x:c r="I29" s="22" t="str"/>
       <x:c r="J29" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1598,7 +1566,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F30" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G30" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -1633,7 +1601,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F31" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G31" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -1641,9 +1609,7 @@
       <x:c r="H31" s="22" t="n">
         <x:v>46215</x:v>
       </x:c>
-      <x:c r="I31" s="22" t="n">
-        <x:v>46219</x:v>
-      </x:c>
+      <x:c r="I31" s="22" t="str"/>
       <x:c r="J31" s="25" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -1676,9 +1642,7 @@
       <x:c r="H32" s="22" t="n">
         <x:v>46220</x:v>
       </x:c>
-      <x:c r="I32" s="22" t="n">
-        <x:v>46217</x:v>
-      </x:c>
+      <x:c r="I32" s="22" t="str"/>
       <x:c r="J32" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -1703,7 +1667,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F33" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G33" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -1711,9 +1675,7 @@
       <x:c r="H33" s="22" t="n">
         <x:v>46225</x:v>
       </x:c>
-      <x:c r="I33" s="22" t="n">
-        <x:v>46224</x:v>
-      </x:c>
+      <x:c r="I33" s="22" t="str"/>
       <x:c r="J33" s="25" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -1738,7 +1700,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F34" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G34" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -1781,9 +1743,7 @@
       <x:c r="H35" s="22" t="n">
         <x:v>46227</x:v>
       </x:c>
-      <x:c r="I35" s="22" t="n">
-        <x:v>46229</x:v>
-      </x:c>
+      <x:c r="I35" s="22" t="str"/>
       <x:c r="J35" s="25" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -1808,7 +1768,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F36" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G36" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -1816,9 +1776,7 @@
       <x:c r="H36" s="22" t="n">
         <x:v>46232</x:v>
       </x:c>
-      <x:c r="I36" s="22" t="n">
-        <x:v>46227</x:v>
-      </x:c>
+      <x:c r="I36" s="22" t="str"/>
       <x:c r="J36" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -1843,7 +1801,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F37" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G37" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -1851,9 +1809,7 @@
       <x:c r="H37" s="22" t="n">
         <x:v>46237</x:v>
       </x:c>
-      <x:c r="I37" s="22" t="n">
-        <x:v>46234</x:v>
-      </x:c>
+      <x:c r="I37" s="22" t="str"/>
       <x:c r="J37" s="25" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -1913,7 +1869,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F39" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G39" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -1921,9 +1877,7 @@
       <x:c r="H39" s="22" t="n">
         <x:v>46239</x:v>
       </x:c>
-      <x:c r="I39" s="22" t="n">
-        <x:v>46239</x:v>
-      </x:c>
+      <x:c r="I39" s="22" t="str"/>
       <x:c r="J39" s="25" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -1948,7 +1902,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F40" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G40" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -1956,9 +1910,7 @@
       <x:c r="H40" s="22" t="n">
         <x:v>46244</x:v>
       </x:c>
-      <x:c r="I40" s="22" t="n">
-        <x:v>46246</x:v>
-      </x:c>
+      <x:c r="I40" s="22" t="str"/>
       <x:c r="J40" s="25" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -1991,9 +1943,7 @@
       <x:c r="H41" s="22" t="n">
         <x:v>46249</x:v>
       </x:c>
-      <x:c r="I41" s="22" t="n">
-        <x:v>46244</x:v>
-      </x:c>
+      <x:c r="I41" s="22" t="str"/>
       <x:c r="J41" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -2018,7 +1968,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F42" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G42" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -2053,7 +2003,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F43" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G43" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -2061,9 +2011,7 @@
       <x:c r="H43" s="22" t="n">
         <x:v>46251</x:v>
       </x:c>
-      <x:c r="I43" s="22" t="n">
-        <x:v>46249</x:v>
-      </x:c>
+      <x:c r="I43" s="22" t="str"/>
       <x:c r="J43" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -2096,9 +2044,7 @@
       <x:c r="H44" s="22" t="n">
         <x:v>46256</x:v>
       </x:c>
-      <x:c r="I44" s="22" t="n">
-        <x:v>46256</x:v>
-      </x:c>
+      <x:c r="I44" s="22" t="str"/>
       <x:c r="J44" s="25" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -2123,7 +2069,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F45" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G45" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -2131,9 +2077,7 @@
       <x:c r="H45" s="22" t="n">
         <x:v>46261</x:v>
       </x:c>
-      <x:c r="I45" s="22" t="n">
-        <x:v>46254</x:v>
-      </x:c>
+      <x:c r="I45" s="22" t="str"/>
       <x:c r="J45" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -2158,7 +2102,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F46" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G46" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -2201,9 +2145,7 @@
       <x:c r="H47" s="22" t="n">
         <x:v>46263</x:v>
       </x:c>
-      <x:c r="I47" s="22" t="n">
-        <x:v>46259</x:v>
-      </x:c>
+      <x:c r="I47" s="22" t="str"/>
       <x:c r="J47" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -2228,7 +2170,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F48" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G48" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -2236,9 +2178,7 @@
       <x:c r="H48" s="22" t="n">
         <x:v>46268</x:v>
       </x:c>
-      <x:c r="I48" s="22" t="n">
-        <x:v>46266</x:v>
-      </x:c>
+      <x:c r="I48" s="22" t="str"/>
       <x:c r="J48" s="25" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -2263,7 +2203,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F49" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G49" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -2271,9 +2211,7 @@
       <x:c r="H49" s="22" t="n">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="I49" s="22" t="n">
-        <x:v>46273</x:v>
-      </x:c>
+      <x:c r="I49" s="22" t="str"/>
       <x:c r="J49" s="25" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -2333,7 +2271,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F51" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G51" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -2341,9 +2279,7 @@
       <x:c r="H51" s="22" t="n">
         <x:v>46275</x:v>
       </x:c>
-      <x:c r="I51" s="22" t="n">
-        <x:v>46278</x:v>
-      </x:c>
+      <x:c r="I51" s="22" t="str"/>
       <x:c r="J51" s="25" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -2368,7 +2304,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F52" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G52" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -2376,9 +2312,7 @@
       <x:c r="H52" s="22" t="n">
         <x:v>46280</x:v>
       </x:c>
-      <x:c r="I52" s="22" t="n">
-        <x:v>46276</x:v>
-      </x:c>
+      <x:c r="I52" s="22" t="str"/>
       <x:c r="J52" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -2411,9 +2345,7 @@
       <x:c r="H53" s="22" t="n">
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="I53" s="22" t="n">
-        <x:v>46283</x:v>
-      </x:c>
+      <x:c r="I53" s="22" t="str"/>
       <x:c r="J53" s="25" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -2438,7 +2370,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F54" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G54" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -2473,7 +2405,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F55" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G55" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -2481,9 +2413,7 @@
       <x:c r="H55" s="22" t="n">
         <x:v>46287</x:v>
       </x:c>
-      <x:c r="I55" s="22" t="n">
-        <x:v>46288</x:v>
-      </x:c>
+      <x:c r="I55" s="22" t="str"/>
       <x:c r="J55" s="25" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -2516,9 +2446,7 @@
       <x:c r="H56" s="22" t="n">
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="I56" s="22" t="n">
-        <x:v>46286</x:v>
-      </x:c>
+      <x:c r="I56" s="22" t="str"/>
       <x:c r="J56" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -2543,7 +2471,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F57" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G57" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -2551,9 +2479,7 @@
       <x:c r="H57" s="22" t="n">
         <x:v>46297</x:v>
       </x:c>
-      <x:c r="I57" s="22" t="n">
-        <x:v>46293</x:v>
-      </x:c>
+      <x:c r="I57" s="22" t="str"/>
       <x:c r="J57" s="25" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -2578,7 +2504,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F58" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G58" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -2621,9 +2547,7 @@
       <x:c r="H59" s="22" t="n">
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="I59" s="22" t="n">
-        <x:v>46298</x:v>
-      </x:c>
+      <x:c r="I59" s="22" t="str"/>
       <x:c r="J59" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -2648,7 +2572,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F60" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G60" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -2656,9 +2580,7 @@
       <x:c r="H60" s="22" t="n">
         <x:v>46304</x:v>
       </x:c>
-      <x:c r="I60" s="22" t="n">
-        <x:v>46305</x:v>
-      </x:c>
+      <x:c r="I60" s="22" t="str"/>
       <x:c r="J60" s="25" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -2683,7 +2605,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F61" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G61" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -2691,9 +2613,7 @@
       <x:c r="H61" s="22" t="n">
         <x:v>46309</x:v>
       </x:c>
-      <x:c r="I61" s="22" t="n">
-        <x:v>46303</x:v>
-      </x:c>
+      <x:c r="I61" s="22" t="str"/>
       <x:c r="J61" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -2753,7 +2673,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F63" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G63" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -2761,9 +2681,7 @@
       <x:c r="H63" s="22" t="n">
         <x:v>46311</x:v>
       </x:c>
-      <x:c r="I63" s="22" t="n">
-        <x:v>46308</x:v>
-      </x:c>
+      <x:c r="I63" s="22" t="str"/>
       <x:c r="J63" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -2788,7 +2706,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F64" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G64" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -2796,9 +2714,7 @@
       <x:c r="H64" s="22" t="n">
         <x:v>46046</x:v>
       </x:c>
-      <x:c r="I64" s="22" t="n">
-        <x:v>46045</x:v>
-      </x:c>
+      <x:c r="I64" s="22" t="str"/>
       <x:c r="J64" s="25" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -2831,9 +2747,7 @@
       <x:c r="H65" s="22" t="n">
         <x:v>46051</x:v>
       </x:c>
-      <x:c r="I65" s="22" t="n">
-        <x:v>46043</x:v>
-      </x:c>
+      <x:c r="I65" s="22" t="str"/>
       <x:c r="J65" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -2858,7 +2772,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F66" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G66" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -2893,7 +2807,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F67" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G67" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -2901,9 +2815,7 @@
       <x:c r="H67" s="22" t="n">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="I67" s="22" t="n">
-        <x:v>46057</x:v>
-      </x:c>
+      <x:c r="I67" s="22" t="str"/>
       <x:c r="J67" s="25" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -2936,9 +2848,7 @@
       <x:c r="H68" s="22" t="n">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="I68" s="22" t="n">
-        <x:v>46055</x:v>
-      </x:c>
+      <x:c r="I68" s="22" t="str"/>
       <x:c r="J68" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -2963,7 +2873,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F69" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G69" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -2971,9 +2881,7 @@
       <x:c r="H69" s="22" t="n">
         <x:v>46063</x:v>
       </x:c>
-      <x:c r="I69" s="22" t="n">
-        <x:v>46062</x:v>
-      </x:c>
+      <x:c r="I69" s="22" t="str"/>
       <x:c r="J69" s="25" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -2998,7 +2906,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F70" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G70" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -3041,9 +2949,7 @@
       <x:c r="H71" s="22" t="n">
         <x:v>46065</x:v>
       </x:c>
-      <x:c r="I71" s="22" t="n">
-        <x:v>46067</x:v>
-      </x:c>
+      <x:c r="I71" s="22" t="str"/>
       <x:c r="J71" s="25" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -3068,7 +2974,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F72" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G72" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -3076,9 +2982,7 @@
       <x:c r="H72" s="22" t="n">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="I72" s="22" t="n">
-        <x:v>46065</x:v>
-      </x:c>
+      <x:c r="I72" s="22" t="str"/>
       <x:c r="J72" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -3103,7 +3007,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F73" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G73" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -3111,9 +3015,7 @@
       <x:c r="H73" s="22" t="n">
         <x:v>46075</x:v>
       </x:c>
-      <x:c r="I73" s="22" t="n">
-        <x:v>46072</x:v>
-      </x:c>
+      <x:c r="I73" s="22" t="str"/>
       <x:c r="J73" s="25" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -3173,7 +3075,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F75" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G75" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -3181,9 +3083,7 @@
       <x:c r="H75" s="22" t="n">
         <x:v>46077</x:v>
       </x:c>
-      <x:c r="I75" s="22" t="n">
-        <x:v>46077</x:v>
-      </x:c>
+      <x:c r="I75" s="22" t="str"/>
       <x:c r="J75" s="25" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -3208,7 +3108,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F76" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G76" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -3216,9 +3116,7 @@
       <x:c r="H76" s="22" t="n">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="I76" s="22" t="n">
-        <x:v>46084</x:v>
-      </x:c>
+      <x:c r="I76" s="22" t="str"/>
       <x:c r="J76" s="25" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -3251,9 +3149,7 @@
       <x:c r="H77" s="22" t="n">
         <x:v>46087</x:v>
       </x:c>
-      <x:c r="I77" s="22" t="n">
-        <x:v>46082</x:v>
-      </x:c>
+      <x:c r="I77" s="22" t="str"/>
       <x:c r="J77" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -3278,7 +3174,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F78" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G78" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -3313,7 +3209,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F79" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G79" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -3321,9 +3217,7 @@
       <x:c r="H79" s="22" t="n">
         <x:v>46089</x:v>
       </x:c>
-      <x:c r="I79" s="22" t="n">
-        <x:v>46087</x:v>
-      </x:c>
+      <x:c r="I79" s="22" t="str"/>
       <x:c r="J79" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -3356,9 +3250,7 @@
       <x:c r="H80" s="22" t="n">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="I80" s="22" t="n">
-        <x:v>46094</x:v>
-      </x:c>
+      <x:c r="I80" s="22" t="str"/>
       <x:c r="J80" s="25" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -3383,7 +3275,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F81" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G81" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -3391,9 +3283,7 @@
       <x:c r="H81" s="22" t="n">
         <x:v>46099</x:v>
       </x:c>
-      <x:c r="I81" s="22" t="n">
-        <x:v>46092</x:v>
-      </x:c>
+      <x:c r="I81" s="22" t="str"/>
       <x:c r="J81" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -3418,7 +3308,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F82" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G82" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -3461,9 +3351,7 @@
       <x:c r="H83" s="22" t="n">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="I83" s="22" t="n">
-        <x:v>46097</x:v>
-      </x:c>
+      <x:c r="I83" s="22" t="str"/>
       <x:c r="J83" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -3488,7 +3376,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F84" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G84" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -3496,9 +3384,7 @@
       <x:c r="H84" s="22" t="n">
         <x:v>46106</x:v>
       </x:c>
-      <x:c r="I84" s="22" t="n">
-        <x:v>46104</x:v>
-      </x:c>
+      <x:c r="I84" s="22" t="str"/>
       <x:c r="J84" s="25" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -3523,7 +3409,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F85" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G85" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -3531,9 +3417,7 @@
       <x:c r="H85" s="22" t="n">
         <x:v>46111</x:v>
       </x:c>
-      <x:c r="I85" s="22" t="n">
-        <x:v>46111</x:v>
-      </x:c>
+      <x:c r="I85" s="22" t="str"/>
       <x:c r="J85" s="25" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -3593,7 +3477,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F87" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G87" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -3601,9 +3485,7 @@
       <x:c r="H87" s="22" t="n">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="I87" s="22" t="n">
-        <x:v>46116</x:v>
-      </x:c>
+      <x:c r="I87" s="22" t="str"/>
       <x:c r="J87" s="25" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -3628,7 +3510,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F88" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G88" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -3636,9 +3518,7 @@
       <x:c r="H88" s="22" t="n">
         <x:v>46118</x:v>
       </x:c>
-      <x:c r="I88" s="22" t="n">
-        <x:v>46114</x:v>
-      </x:c>
+      <x:c r="I88" s="22" t="str"/>
       <x:c r="J88" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -3671,9 +3551,7 @@
       <x:c r="H89" s="22" t="n">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="I89" s="22" t="n">
-        <x:v>46121</x:v>
-      </x:c>
+      <x:c r="I89" s="22" t="str"/>
       <x:c r="J89" s="25" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -3698,7 +3576,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F90" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G90" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -3733,7 +3611,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F91" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G91" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -3741,9 +3619,7 @@
       <x:c r="H91" s="22" t="n">
         <x:v>46125</x:v>
       </x:c>
-      <x:c r="I91" s="22" t="n">
-        <x:v>46126</x:v>
-      </x:c>
+      <x:c r="I91" s="22" t="str"/>
       <x:c r="J91" s="25" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -3776,9 +3652,7 @@
       <x:c r="H92" s="22" t="n">
         <x:v>46130</x:v>
       </x:c>
-      <x:c r="I92" s="22" t="n">
-        <x:v>46124</x:v>
-      </x:c>
+      <x:c r="I92" s="22" t="str"/>
       <x:c r="J92" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -3803,7 +3677,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F93" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G93" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -3811,9 +3685,7 @@
       <x:c r="H93" s="22" t="n">
         <x:v>46135</x:v>
       </x:c>
-      <x:c r="I93" s="22" t="n">
-        <x:v>46131</x:v>
-      </x:c>
+      <x:c r="I93" s="22" t="str"/>
       <x:c r="J93" s="25" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -3838,7 +3710,7 @@
         <x:v>Unit B</x:v>
       </x:c>
       <x:c r="F94" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G94" s="18" t="str">
         <x:v>Selesai</x:v>
@@ -3881,9 +3753,7 @@
       <x:c r="H95" s="22" t="n">
         <x:v>46137</x:v>
       </x:c>
-      <x:c r="I95" s="22" t="n">
-        <x:v>46136</x:v>
-      </x:c>
+      <x:c r="I95" s="22" t="str"/>
       <x:c r="J95" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -3908,7 +3778,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F96" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G96" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -3916,9 +3786,7 @@
       <x:c r="H96" s="22" t="n">
         <x:v>46142</x:v>
       </x:c>
-      <x:c r="I96" s="22" t="n">
-        <x:v>46143</x:v>
-      </x:c>
+      <x:c r="I96" s="22" t="str"/>
       <x:c r="J96" s="25" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -3943,7 +3811,7 @@
         <x:v>Unit A</x:v>
       </x:c>
       <x:c r="F97" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G97" s="18" t="str">
         <x:v>Ditunda</x:v>
@@ -3951,9 +3819,7 @@
       <x:c r="H97" s="22" t="n">
         <x:v>46147</x:v>
       </x:c>
-      <x:c r="I97" s="22" t="n">
-        <x:v>46141</x:v>
-      </x:c>
+      <x:c r="I97" s="22" t="str"/>
       <x:c r="J97" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -4013,7 +3879,7 @@
         <x:v>Unit C</x:v>
       </x:c>
       <x:c r="F99" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Sedang</x:v>
       </x:c>
       <x:c r="G99" s="18" t="str">
         <x:v>Diproses</x:v>
@@ -4021,9 +3887,7 @@
       <x:c r="H99" s="22" t="n">
         <x:v>46149</x:v>
       </x:c>
-      <x:c r="I99" s="22" t="n">
-        <x:v>46146</x:v>
-      </x:c>
+      <x:c r="I99" s="22" t="str"/>
       <x:c r="J99" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -4048,7 +3912,7 @@
         <x:v>Unit D</x:v>
       </x:c>
       <x:c r="F100" s="18" t="str">
-        <x:v>Tinggi</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="G100" s="18" t="str">
         <x:v>Menunggu Arahan</x:v>
@@ -4056,9 +3920,7 @@
       <x:c r="H100" s="22" t="n">
         <x:v>46154</x:v>
       </x:c>
-      <x:c r="I100" s="22" t="n">
-        <x:v>46153</x:v>
-      </x:c>
+      <x:c r="I100" s="22" t="str"/>
       <x:c r="J100" s="25" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -4091,9 +3953,7 @@
       <x:c r="H101" s="23" t="n">
         <x:v>46159</x:v>
       </x:c>
-      <x:c r="I101" s="23" t="n">
-        <x:v>46151</x:v>
-      </x:c>
+      <x:c r="I101" s="23" t="str"/>
       <x:c r="J101" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4104,7 +3964,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc30fc39cb7c449f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65c1fcf38a744033"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4161,8 +4021,8 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
-      <x:c r="A7" s="44" t="str">
-        <x:v>Catatan</x:v>
+      <x:c r="A7" s="43" t="str">
+        <x:v>Tanggal_Masuk</x:v>
       </x:c>
       <x:c r="B7" s="43" t="str">
         <x:v>2026-03-12</x:v>
@@ -4245,7 +4105,7 @@
         <x:v>2026-03-16</x:v>
       </x:c>
       <x:c r="C14" s="43" t="str">
-        <x:v>Kosong bila belum selesai. Dataset dummy sudah diisi untuk kebutuhan latihan.</x:v>
+        <x:v>Tanggal selesai hanya diisi bila Status_Disposisi = Selesai; selain itu harus kosong.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="38" customHeight="1">
@@ -4269,11 +4129,19 @@
       <x:c r="C16" s="43" t="str">
         <x:v>Catatan umum tanpa isi surat atau informasi rahasia.</x:v>
       </x:c>
+    </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" s="47" t="str">
+        <x:v>Catatan: gunakan data sintetis selama latihan dan jangan memasukkan data pribadi ke ChatGPT.</x:v>
+      </x:c>
+      <x:c r="B17" s="47"/>
+      <x:c r="C17" s="47"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A3:F3"/>
+    <x:mergeCell ref="A17:C17"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
